--- a/fix-errors/ig/FRSectionProceduresLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRSectionProceduresLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-procedures</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-procedures|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-historique-des-actes</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-historique-des-actes|0.1.0</t>
   </si>
   <si>
     <t>FRLMProcedures</t>
@@ -142,7 +142,7 @@
     <t>FRCDAHistoriqueDesActes.entry:FRCDAActe</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
     <t>FRCompositionDocument.section:sectionProceduresHx</t>
